--- a/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_20_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_20_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.249971</v>
+        <v>0.249952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         <v>0.671096</v>
       </c>
       <c r="J2" t="n">
-        <v>0.250178</v>
+        <v>0.250238</v>
       </c>
       <c r="K2" t="n">
         <v>0.485</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_11.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_1.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.249932</v>
+        <v>0.249937</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>0.671096</v>
       </c>
       <c r="J3" t="n">
-        <v>0.250225</v>
+        <v>0.250203</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_4.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_6.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,7 +783,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249954</v>
+        <v>0.249924</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>0.671096</v>
       </c>
       <c r="J4" t="n">
-        <v>0.250146</v>
+        <v>0.250215</v>
       </c>
       <c r="K4" t="n">
         <v>0.485</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_9.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_0.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -884,7 +884,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.18025</v>
+        <v>0.09064</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.751669</v>
+        <v>0.893432</v>
       </c>
       <c r="H5" t="n">
-        <v>0.696782</v>
+        <v>0.892327</v>
       </c>
       <c r="I5" t="n">
-        <v>0.723186</v>
+        <v>0.892879</v>
       </c>
       <c r="J5" t="n">
-        <v>0.188535</v>
+        <v>0.089208</v>
       </c>
       <c r="K5" t="n">
-        <v>0.719298</v>
+        <v>0.917582</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6340209999999999</v>
+        <v>0.860825</v>
       </c>
       <c r="M5" t="n">
-        <v>0.673973</v>
+        <v>0.888298</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_3.txt</t>
+          <t>_4_20_1_1790733681_2.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.249952</v>
+        <v>0.124444</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E7" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.505</v>
+        <v>0.808841</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.837871</v>
       </c>
       <c r="I7" t="n">
-        <v>0.671096</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.250221</v>
+        <v>0.135687</v>
       </c>
       <c r="K7" t="n">
-        <v>0.485</v>
+        <v>0.770732</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.814433</v>
       </c>
       <c r="M7" t="n">
-        <v>0.653199</v>
+        <v>0.79198</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_8.txt</t>
+          <t>_4_20_1_1790733681_18.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,7 +1187,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.078568</v>
+        <v>0.082245</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9202</v>
+        <v>0.9096610000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.913366</v>
+        <v>0.897277</v>
       </c>
       <c r="I8" t="n">
-        <v>0.91677</v>
+        <v>0.903427</v>
       </c>
       <c r="J8" t="n">
-        <v>0.080705</v>
+        <v>0.082054</v>
       </c>
       <c r="K8" t="n">
-        <v>0.934426</v>
+        <v>0.902564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.881443</v>
+        <v>0.907216</v>
       </c>
       <c r="M8" t="n">
-        <v>0.907162</v>
+        <v>0.904884</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_8.txt</t>
+          <t>_4_20_1_1790733681_12.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1288,42 +1288,42 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249924</v>
+        <v>0.078568</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.505</v>
+        <v>0.9202</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.913366</v>
       </c>
       <c r="I9" t="n">
-        <v>0.671096</v>
+        <v>0.91677</v>
       </c>
       <c r="J9" t="n">
-        <v>0.250215</v>
+        <v>0.080705</v>
       </c>
       <c r="K9" t="n">
-        <v>0.485</v>
+        <v>0.934426</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.881443</v>
       </c>
       <c r="M9" t="n">
-        <v>0.653199</v>
+        <v>0.907162</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,28 +1359,28 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_0.txt</t>
+          <t>_4_20_1_1790733681_8.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
       </c>
       <c r="AA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.249925</v>
+        <v>0.249953</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>0.671096</v>
       </c>
       <c r="J10" t="n">
-        <v>0.250219</v>
+        <v>0.250187</v>
       </c>
       <c r="K10" t="n">
         <v>0.485</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_17.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_5.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,42 +1490,42 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.09064</v>
+        <v>0.249946</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.893432</v>
+        <v>0.505</v>
       </c>
       <c r="H11" t="n">
-        <v>0.892327</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.892879</v>
+        <v>0.671096</v>
       </c>
       <c r="J11" t="n">
-        <v>0.089208</v>
+        <v>0.250175</v>
       </c>
       <c r="K11" t="n">
-        <v>0.917582</v>
+        <v>0.485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.860825</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0.888298</v>
+        <v>0.653199</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,28 +1561,28 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_2.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_15.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.074299</v>
+        <v>0.249933</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.899633</v>
+        <v>0.505</v>
       </c>
       <c r="H12" t="n">
-        <v>0.909653</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9046149999999999</v>
+        <v>0.671096</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08198800000000001</v>
+        <v>0.250202</v>
       </c>
       <c r="K12" t="n">
-        <v>0.888298</v>
+        <v>0.485</v>
       </c>
       <c r="L12" t="n">
-        <v>0.860825</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.874346</v>
+        <v>0.653199</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,28 +1662,28 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_7.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_3.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>20</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.249878</v>
+        <v>0.084309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E13" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.502522</v>
+        <v>0.908189</v>
       </c>
       <c r="H13" t="n">
-        <v>0.986386</v>
+        <v>0.905941</v>
       </c>
       <c r="I13" t="n">
-        <v>0.665831</v>
+        <v>0.907063</v>
       </c>
       <c r="J13" t="n">
-        <v>0.250248</v>
+        <v>0.088048</v>
       </c>
       <c r="K13" t="n">
-        <v>0.479798</v>
+        <v>0.871795</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9793809999999999</v>
+        <v>0.876289</v>
       </c>
       <c r="M13" t="n">
-        <v>0.644068</v>
+        <v>0.874036</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,28 +1763,28 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_13.txt</t>
+          <t>_4_20_1_1790733681_10.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>20</v>
       </c>
       <c r="AA13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -1793,42 +1793,42 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.249947</v>
+        <v>0.15136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E14" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.505</v>
+        <v>0.779874</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.767327</v>
       </c>
       <c r="I14" t="n">
-        <v>0.671096</v>
+        <v>0.77355</v>
       </c>
       <c r="J14" t="n">
-        <v>0.250216</v>
+        <v>0.155781</v>
       </c>
       <c r="K14" t="n">
-        <v>0.485</v>
+        <v>0.789189</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.7525770000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.653199</v>
+        <v>0.7704490000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_14.txt</t>
+          <t>_4_20_1_1790733681_19.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>20</v>
       </c>
       <c r="AA14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.249953</v>
+        <v>0.249878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.505</v>
+        <v>0.502522</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.986386</v>
       </c>
       <c r="I15" t="n">
-        <v>0.671096</v>
+        <v>0.665831</v>
       </c>
       <c r="J15" t="n">
-        <v>0.250187</v>
+        <v>0.250248</v>
       </c>
       <c r="K15" t="n">
-        <v>0.485</v>
+        <v>0.479798</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.9793809999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.653199</v>
+        <v>0.644068</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_5.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_13.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -1995,42 +1995,42 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.249918</v>
+        <v>0.132663</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E16" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.505</v>
+        <v>0.84585</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.794554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.671096</v>
+        <v>0.8194</v>
       </c>
       <c r="J16" t="n">
-        <v>0.250244</v>
+        <v>0.129254</v>
       </c>
       <c r="K16" t="n">
-        <v>0.485</v>
+        <v>0.82199</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0.8092780000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.653199</v>
+        <v>0.815584</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,23 +2066,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_18.txt</t>
+          <t>_4_20_1_1790733681_1.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z16" t="n">
         <v>20</v>
       </c>
       <c r="AA16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.124444</v>
+        <v>0.084894</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.808841</v>
+        <v>0.91468</v>
       </c>
       <c r="H17" t="n">
-        <v>0.837871</v>
+        <v>0.902228</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.908411</v>
       </c>
       <c r="J17" t="n">
-        <v>0.135687</v>
+        <v>0.089016</v>
       </c>
       <c r="K17" t="n">
-        <v>0.770732</v>
+        <v>0.867347</v>
       </c>
       <c r="L17" t="n">
-        <v>0.814433</v>
+        <v>0.876289</v>
       </c>
       <c r="M17" t="n">
-        <v>0.79198</v>
+        <v>0.871795</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_18.txt</t>
+          <t>_4_20_1_1790733681_9.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -2197,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.140669</v>
+        <v>0.249918</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.828309</v>
+        <v>0.505</v>
       </c>
       <c r="H18" t="n">
-        <v>0.782178</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.804583</v>
+        <v>0.671096</v>
       </c>
       <c r="J18" t="n">
-        <v>0.136561</v>
+        <v>0.250244</v>
       </c>
       <c r="K18" t="n">
-        <v>0.847826</v>
+        <v>0.485</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8041239999999999</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.825397</v>
+        <v>0.653199</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_6.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_18.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>20</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>0.671096</v>
       </c>
       <c r="J19" t="n">
-        <v>0.250238</v>
+        <v>0.250221</v>
       </c>
       <c r="K19" t="n">
         <v>0.485</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_1.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_8.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.249937</v>
+        <v>0.249971</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>0.671096</v>
       </c>
       <c r="J20" t="n">
-        <v>0.250203</v>
+        <v>0.250178</v>
       </c>
       <c r="K20" t="n">
         <v>0.485</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_6.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_11.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,42 +2500,42 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.249946</v>
+        <v>0.116522</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E21" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.505</v>
+        <v>0.840438</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.8539600000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.671096</v>
+        <v>0.847145</v>
       </c>
       <c r="J21" t="n">
-        <v>0.250175</v>
+        <v>0.126645</v>
       </c>
       <c r="K21" t="n">
-        <v>0.485</v>
+        <v>0.810256</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.814433</v>
       </c>
       <c r="M21" t="n">
-        <v>0.653199</v>
+        <v>0.812339</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,23 +2571,23 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_15.txt</t>
+          <t>_4_20_1_1790733681_5.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z21" t="n">
         <v>20</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.249927</v>
+        <v>0.249907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>0.671096</v>
       </c>
       <c r="J22" t="n">
-        <v>0.250195</v>
+        <v>0.250203</v>
       </c>
       <c r="K22" t="n">
         <v>0.485</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_10.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_19.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.249981</v>
+        <v>0.18025</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E23" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.505</v>
+        <v>0.751669</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.696782</v>
       </c>
       <c r="I23" t="n">
-        <v>0.671096</v>
+        <v>0.723186</v>
       </c>
       <c r="J23" t="n">
-        <v>0.250177</v>
+        <v>0.188535</v>
       </c>
       <c r="K23" t="n">
-        <v>0.485</v>
+        <v>0.719298</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.6340209999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.653199</v>
+        <v>0.673973</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_12.txt</t>
+          <t>_4_20_1_1790733681_3.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>20</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,42 +2803,42 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.249936</v>
+        <v>0.139911</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E24" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.505</v>
+        <v>0.799499</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.789604</v>
       </c>
       <c r="I24" t="n">
-        <v>0.671096</v>
+        <v>0.79452</v>
       </c>
       <c r="J24" t="n">
-        <v>0.250228</v>
+        <v>0.139523</v>
       </c>
       <c r="K24" t="n">
-        <v>0.485</v>
+        <v>0.785714</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.793814</v>
       </c>
       <c r="M24" t="n">
-        <v>0.653199</v>
+        <v>0.789744</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,23 +2874,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_2.txt</t>
+          <t>_4_20_1_1790733681_17.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>20</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.082245</v>
+        <v>0.249947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9096610000000001</v>
+        <v>0.505</v>
       </c>
       <c r="H25" t="n">
-        <v>0.897277</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.903427</v>
+        <v>0.671096</v>
       </c>
       <c r="J25" t="n">
-        <v>0.082054</v>
+        <v>0.250216</v>
       </c>
       <c r="K25" t="n">
-        <v>0.902564</v>
+        <v>0.485</v>
       </c>
       <c r="L25" t="n">
-        <v>0.907216</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.904884</v>
+        <v>0.653199</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,28 +2975,28 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_12.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_14.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>20</v>
       </c>
       <c r="AA25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.11189</v>
+        <v>0.249936</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8430879999999999</v>
+        <v>0.505</v>
       </c>
       <c r="H26" t="n">
-        <v>0.837871</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.840472</v>
+        <v>0.671096</v>
       </c>
       <c r="J26" t="n">
-        <v>0.123457</v>
+        <v>0.250228</v>
       </c>
       <c r="K26" t="n">
-        <v>0.820106</v>
+        <v>0.485</v>
       </c>
       <c r="L26" t="n">
-        <v>0.798969</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.809399</v>
+        <v>0.653199</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_15.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_2.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>20</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,42 +3106,42 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.15136</v>
+        <v>0.249954</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.779874</v>
+        <v>0.505</v>
       </c>
       <c r="H27" t="n">
-        <v>0.767327</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.77355</v>
+        <v>0.671096</v>
       </c>
       <c r="J27" t="n">
-        <v>0.155781</v>
+        <v>0.250146</v>
       </c>
       <c r="K27" t="n">
-        <v>0.789189</v>
+        <v>0.485</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7525770000000001</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7704490000000001</v>
+        <v>0.653199</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,23 +3177,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_19.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_9.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>20</v>
       </c>
       <c r="AA27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.09843</v>
+        <v>0.099777</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.904516</v>
+        <v>0.898263</v>
       </c>
       <c r="H28" t="n">
-        <v>0.867574</v>
+        <v>0.8960399999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.88566</v>
+        <v>0.89715</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1006</v>
+        <v>0.101931</v>
       </c>
       <c r="K28" t="n">
-        <v>0.889474</v>
+        <v>0.887701</v>
       </c>
       <c r="L28" t="n">
-        <v>0.871134</v>
+        <v>0.85567</v>
       </c>
       <c r="M28" t="n">
-        <v>0.880208</v>
+        <v>0.871391</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_11.txt</t>
+          <t>_4_20_1_1790733681_4.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.139911</v>
+        <v>0.08826000000000001</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.799499</v>
+        <v>0.892902</v>
       </c>
       <c r="H29" t="n">
-        <v>0.789604</v>
+        <v>0.8873760000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.79452</v>
+        <v>0.89013</v>
       </c>
       <c r="J29" t="n">
-        <v>0.139523</v>
+        <v>0.09793399999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.785714</v>
+        <v>0.857143</v>
       </c>
       <c r="L29" t="n">
-        <v>0.793814</v>
+        <v>0.8659790000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>0.789744</v>
+        <v>0.861538</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_17.txt</t>
+          <t>_4_20_1_1790733681_14.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.249933</v>
+        <v>0.249954</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>0.671096</v>
       </c>
       <c r="J30" t="n">
-        <v>0.250202</v>
+        <v>0.250185</v>
       </c>
       <c r="K30" t="n">
         <v>0.485</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_3.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_16.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3510,7 +3510,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.099777</v>
+        <v>0.116312</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3527,25 +3527,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.898263</v>
+        <v>0.844893</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8960399999999999</v>
+        <v>0.8292079999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.89715</v>
+        <v>0.836977</v>
       </c>
       <c r="J31" t="n">
-        <v>0.101931</v>
+        <v>0.111592</v>
       </c>
       <c r="K31" t="n">
-        <v>0.887701</v>
+        <v>0.8375629999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>0.85567</v>
+        <v>0.850515</v>
       </c>
       <c r="M31" t="n">
-        <v>0.871391</v>
+        <v>0.84399</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_4.txt</t>
+          <t>_4_20_1_1790733681_16.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.132663</v>
+        <v>0.11189</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.84585</v>
+        <v>0.8430879999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.794554</v>
+        <v>0.837871</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8194</v>
+        <v>0.840472</v>
       </c>
       <c r="J32" t="n">
-        <v>0.129254</v>
+        <v>0.123457</v>
       </c>
       <c r="K32" t="n">
-        <v>0.82199</v>
+        <v>0.820106</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8092780000000001</v>
+        <v>0.798969</v>
       </c>
       <c r="M32" t="n">
-        <v>0.815584</v>
+        <v>0.809399</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_1.txt</t>
+          <t>_4_20_1_1790733681_15.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.249954</v>
+        <v>0.249932</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>0.671096</v>
       </c>
       <c r="J33" t="n">
-        <v>0.250185</v>
+        <v>0.250225</v>
       </c>
       <c r="K33" t="n">
         <v>0.485</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_16.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_4.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.08826000000000001</v>
+        <v>0.074299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.892902</v>
+        <v>0.899633</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8873760000000001</v>
+        <v>0.909653</v>
       </c>
       <c r="I34" t="n">
-        <v>0.89013</v>
+        <v>0.9046149999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0.09793399999999999</v>
+        <v>0.08198800000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.857143</v>
+        <v>0.888298</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8659790000000001</v>
+        <v>0.860825</v>
       </c>
       <c r="M34" t="n">
-        <v>0.861538</v>
+        <v>0.874346</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_14.txt</t>
+          <t>_4_20_1_1790733681_7.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3914,42 +3914,42 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.084309</v>
+        <v>0.249925</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E35" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.908189</v>
+        <v>0.505</v>
       </c>
       <c r="H35" t="n">
-        <v>0.905941</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.907063</v>
+        <v>0.671096</v>
       </c>
       <c r="J35" t="n">
-        <v>0.088048</v>
+        <v>0.250219</v>
       </c>
       <c r="K35" t="n">
-        <v>0.871795</v>
+        <v>0.485</v>
       </c>
       <c r="L35" t="n">
-        <v>0.876289</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.874036</v>
+        <v>0.653199</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_10.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_17.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>20</v>
       </c>
       <c r="AA35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4015,42 +4015,42 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.116312</v>
+        <v>0.249927</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E36" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F36" t="n">
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.844893</v>
+        <v>0.505</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8292079999999999</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0.836977</v>
+        <v>0.671096</v>
       </c>
       <c r="J36" t="n">
-        <v>0.111592</v>
+        <v>0.250195</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8375629999999999</v>
+        <v>0.485</v>
       </c>
       <c r="L36" t="n">
-        <v>0.850515</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0.84399</v>
+        <v>0.653199</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,23 +4086,23 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_16.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_10.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z36" t="n">
         <v>20</v>
       </c>
       <c r="AA36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4116,7 +4116,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.116522</v>
+        <v>0.140669</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.840438</v>
+        <v>0.828309</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8539600000000001</v>
+        <v>0.782178</v>
       </c>
       <c r="I37" t="n">
-        <v>0.847145</v>
+        <v>0.804583</v>
       </c>
       <c r="J37" t="n">
-        <v>0.126645</v>
+        <v>0.136561</v>
       </c>
       <c r="K37" t="n">
-        <v>0.810256</v>
+        <v>0.847826</v>
       </c>
       <c r="L37" t="n">
-        <v>0.814433</v>
+        <v>0.8041239999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.812339</v>
+        <v>0.825397</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_5.txt</t>
+          <t>_4_20_1_1790733681_6.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.092303</v>
+        <v>0.110165</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4234,25 +4234,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.89612</v>
+        <v>0.849568</v>
       </c>
       <c r="H38" t="n">
-        <v>0.886139</v>
+        <v>0.852723</v>
       </c>
       <c r="I38" t="n">
-        <v>0.891101</v>
+        <v>0.851143</v>
       </c>
       <c r="J38" t="n">
-        <v>0.098177</v>
+        <v>0.110127</v>
       </c>
       <c r="K38" t="n">
-        <v>0.860825</v>
+        <v>0.832487</v>
       </c>
       <c r="L38" t="n">
-        <v>0.860825</v>
+        <v>0.845361</v>
       </c>
       <c r="M38" t="n">
-        <v>0.860825</v>
+        <v>0.838875</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_0.txt</t>
+          <t>_4_20_1_1790733681_13.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.084894</v>
+        <v>0.09843</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4335,25 +4335,25 @@
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.91468</v>
+        <v>0.904516</v>
       </c>
       <c r="H39" t="n">
-        <v>0.902228</v>
+        <v>0.867574</v>
       </c>
       <c r="I39" t="n">
-        <v>0.908411</v>
+        <v>0.88566</v>
       </c>
       <c r="J39" t="n">
-        <v>0.089016</v>
+        <v>0.1006</v>
       </c>
       <c r="K39" t="n">
-        <v>0.867347</v>
+        <v>0.889474</v>
       </c>
       <c r="L39" t="n">
-        <v>0.876289</v>
+        <v>0.871134</v>
       </c>
       <c r="M39" t="n">
-        <v>0.871795</v>
+        <v>0.880208</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_9.txt</t>
+          <t>_4_20_1_1790733681_11.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4419,42 +4419,42 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.249907</v>
+        <v>0.092303</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_</t>
+          <t>_4_20_1_</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1790733748</v>
+        <v>1790733681</v>
       </c>
       <c r="E40" t="n">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F40" t="n">
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.505</v>
+        <v>0.89612</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0.886139</v>
       </c>
       <c r="I40" t="n">
-        <v>0.671096</v>
+        <v>0.891101</v>
       </c>
       <c r="J40" t="n">
-        <v>0.250203</v>
+        <v>0.098177</v>
       </c>
       <c r="K40" t="n">
-        <v>0.485</v>
+        <v>0.860825</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0.860825</v>
       </c>
       <c r="M40" t="n">
-        <v>0.653199</v>
+        <v>0.860825</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,28 +4490,28 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_1_1790733748_19.txt</t>
+          <t>_4_20_1_1790733681_0.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5]</t>
+          <t>[20]</t>
         </is>
       </c>
       <c r="Z40" t="n">
         <v>20</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.110165</v>
+        <v>0.249981</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_4_20_1_</t>
+          <t>_4_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790733681</v>
+        <v>1790733748</v>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.849568</v>
+        <v>0.505</v>
       </c>
       <c r="H41" t="n">
-        <v>0.852723</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.851143</v>
+        <v>0.671096</v>
       </c>
       <c r="J41" t="n">
-        <v>0.110127</v>
+        <v>0.250177</v>
       </c>
       <c r="K41" t="n">
-        <v>0.832487</v>
+        <v>0.485</v>
       </c>
       <c r="L41" t="n">
-        <v>0.845361</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.838875</v>
+        <v>0.653199</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_4_20_1_1790733681_13.txt</t>
+          <t>_4_5_5_5_5_1_1790733748_12.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>20</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4682,7 +4682,7 @@
         <v>0.83831065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05506310660197555</v>
+        <v>0.05506310660197557</v>
       </c>
       <c r="D2" t="n">
         <v>0.907162</v>
